--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28985-2026 artfynd.xlsx
+++ b/artfynd/A 28985-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136482374</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136482375</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
